--- a/data/Lifecycle_upgrade.xlsx
+++ b/data/Lifecycle_upgrade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSP1001461\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E947FC7-AFF8-4559-BE6E-B90E054DE4FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386237BC-357F-4111-A69F-99393E71D0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -854,7 +854,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>

--- a/data/Lifecycle_upgrade.xlsx
+++ b/data/Lifecycle_upgrade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSP1001461\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{386237BC-357F-4111-A69F-99393E71D0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6C1EE2-3417-46B7-A2AB-3C2EE0C2327A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -764,7 +764,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>21</v>
       </c>
@@ -806,7 +806,7 @@
       <c r="G9" s="7"/>
       <c r="H9" s="10"/>
     </row>
-    <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="20"/>
       <c r="B10" s="6" t="s">
         <v>27</v>

--- a/data/Lifecycle_upgrade.xlsx
+++ b/data/Lifecycle_upgrade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PSP1001461\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6C1EE2-3417-46B7-A2AB-3C2EE0C2327A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D4FC79C-F092-43D5-8571-DE82BD4BC78D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -854,7 +854,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F12" s="9">
         <v>0</v>
